--- a/model_tracker.xlsx
+++ b/model_tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16.83203125" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,16 @@
           <t>2026-04-12 14:59</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:46</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-04-24 23:19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +485,12 @@
       <c r="F2" s="1" t="n">
         <v>0.9873190522193909</v>
       </c>
+      <c r="G2" s="1" t="n">
+        <v>0.9404253363609314</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.9404253363609314</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -499,6 +515,12 @@
       <c r="F3" s="1" t="n">
         <v>0.878627598285675</v>
       </c>
+      <c r="G3" s="1" t="n">
+        <v>0.947868824005127</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.947868824005127</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +545,12 @@
       <c r="F4" s="1" t="n">
         <v>0.9960981607437134</v>
       </c>
+      <c r="G4" s="1" t="n">
+        <v>0.9809999465942383</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.9809999465942383</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,6 +575,12 @@
       <c r="F5" s="1" t="n">
         <v>0.988421618938446</v>
       </c>
+      <c r="G5" s="1" t="n">
+        <v>0.930782675743103</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.930782675743103</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -571,6 +605,12 @@
       <c r="F6" s="1" t="n">
         <v>0.9664163589477539</v>
       </c>
+      <c r="G6" s="1" t="n">
+        <v>0.5897333025932312</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.5897333025932312</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -595,6 +635,12 @@
       <c r="F7" s="1" t="n">
         <v>0.9828280210494995</v>
       </c>
+      <c r="G7" s="1" t="n">
+        <v>0.9483872056007385</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.9483872056007385</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,6 +665,12 @@
       <c r="F8" s="1" t="n">
         <v>0.9953747391700745</v>
       </c>
+      <c r="G8" s="1" t="n">
+        <v>0.8935146927833557</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.8935146927833557</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -643,6 +695,12 @@
       <c r="F9" s="1" t="n">
         <v>0.6967057585716248</v>
       </c>
+      <c r="G9" s="1" t="n">
+        <v>0.7253397703170776</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.7253397703170776</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -669,6 +727,12 @@
       <c r="F10" s="1" t="n">
         <v>0.9220098853111267</v>
       </c>
+      <c r="G10" s="1" t="n">
+        <v>0.5560612082481384</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.5560612082481384</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +757,12 @@
       <c r="F11" s="1" t="n">
         <v>0.4804774224758148</v>
       </c>
+      <c r="G11" s="1" t="n">
+        <v>0.9816820025444031</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.9816820025444031</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -717,6 +787,12 @@
       <c r="F12" s="1" t="n">
         <v>0.5751557946205139</v>
       </c>
+      <c r="G12" s="1" t="n">
+        <v>0.9661639332771301</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.9661639332771301</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -747,6 +823,16 @@
           <t>incorrect</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -771,6 +857,12 @@
       <c r="F14" s="1" t="n">
         <v>0.8526699542999268</v>
       </c>
+      <c r="G14" s="1" t="n">
+        <v>0.8259350061416626</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.8259350061416626</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -795,6 +887,12 @@
       <c r="F15" s="1" t="n">
         <v>0.4085508286952972</v>
       </c>
+      <c r="G15" s="1" t="n">
+        <v>0.9435409307479858</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0.9435409307479858</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -819,6 +917,12 @@
       <c r="F16" s="1" t="n">
         <v>0.8142808079719543</v>
       </c>
+      <c r="G16" s="1" t="n">
+        <v>0.8595859408378601</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.8595859408378601</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,6 +946,12 @@
       </c>
       <c r="F17" s="1" t="n">
         <v>0.9935890436172485</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.9355594515800476</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.9355594515800476</v>
       </c>
     </row>
   </sheetData>
